--- a/artfynd/A 48764-2025 artfynd.xlsx
+++ b/artfynd/A 48764-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129452917</v>
       </c>
       <c r="B2" t="n">
-        <v>98710</v>
+        <v>98712</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1301,7 +1301,7 @@
         <v>129452912</v>
       </c>
       <c r="B7" t="n">
-        <v>92261</v>
+        <v>92263</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1544,7 +1544,7 @@
         <v>129452920</v>
       </c>
       <c r="B9" t="n">
-        <v>98710</v>
+        <v>98712</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 48764-2025 artfynd.xlsx
+++ b/artfynd/A 48764-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129452917</v>
       </c>
       <c r="B2" t="n">
-        <v>98712</v>
+        <v>98716</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -801,10 +801,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129453566</v>
+        <v>129453553</v>
       </c>
       <c r="B3" t="n">
-        <v>4773</v>
+        <v>58097</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -812,32 +812,36 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100299</v>
+        <v>103015</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Thomsons trägnagare</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Cacotemnus thomsoni</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Kraatz, 1881)</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>ex.</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>adult</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
@@ -851,13 +855,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>473998</v>
+        <v>473651</v>
       </c>
       <c r="R3" t="n">
-        <v>6424257</v>
+        <v>6424350</v>
       </c>
       <c r="S3" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -886,7 +890,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>13:28</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -896,7 +900,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>13:28</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -923,10 +927,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129453553</v>
+        <v>129453566</v>
       </c>
       <c r="B4" t="n">
-        <v>58097</v>
+        <v>4773</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -934,36 +938,32 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103015</v>
+        <v>100299</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Thomsons trägnagare</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Cacotemnus thomsoni</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>adult</t>
+          <t>(Kraatz, 1881)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>ex.</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
@@ -977,13 +977,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>473651</v>
+        <v>473998</v>
       </c>
       <c r="R4" t="n">
-        <v>6424350</v>
+        <v>6424257</v>
       </c>
       <c r="S4" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1012,7 +1012,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>13:28</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1022,7 +1022,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>13:28</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1301,7 +1301,7 @@
         <v>129452912</v>
       </c>
       <c r="B7" t="n">
-        <v>92263</v>
+        <v>92267</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1544,7 +1544,7 @@
         <v>129452920</v>
       </c>
       <c r="B9" t="n">
-        <v>98712</v>
+        <v>98716</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 48764-2025 artfynd.xlsx
+++ b/artfynd/A 48764-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129452917</v>
       </c>
       <c r="B2" t="n">
-        <v>98716</v>
+        <v>98724</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1301,7 +1301,7 @@
         <v>129452912</v>
       </c>
       <c r="B7" t="n">
-        <v>92267</v>
+        <v>92268</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1544,7 +1544,7 @@
         <v>129452920</v>
       </c>
       <c r="B9" t="n">
-        <v>98716</v>
+        <v>98724</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 48764-2025 artfynd.xlsx
+++ b/artfynd/A 48764-2025 artfynd.xlsx
@@ -801,10 +801,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129453553</v>
+        <v>129453566</v>
       </c>
       <c r="B3" t="n">
-        <v>58097</v>
+        <v>4773</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -812,36 +812,32 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103015</v>
+        <v>100299</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Thomsons trägnagare</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Cacotemnus thomsoni</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>adult</t>
+          <t>(Kraatz, 1881)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>ex.</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
@@ -855,13 +851,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>473651</v>
+        <v>473998</v>
       </c>
       <c r="R3" t="n">
-        <v>6424350</v>
+        <v>6424257</v>
       </c>
       <c r="S3" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -890,7 +886,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>13:28</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -900,7 +896,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>13:28</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -927,10 +923,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129453566</v>
+        <v>129453553</v>
       </c>
       <c r="B4" t="n">
-        <v>4773</v>
+        <v>58097</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -938,32 +934,36 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100299</v>
+        <v>103015</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Thomsons trägnagare</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Cacotemnus thomsoni</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Kraatz, 1881)</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>ex.</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>adult</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
@@ -977,13 +977,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>473998</v>
+        <v>473651</v>
       </c>
       <c r="R4" t="n">
-        <v>6424257</v>
+        <v>6424350</v>
       </c>
       <c r="S4" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1012,7 +1012,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>13:28</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1022,7 +1022,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>13:28</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AD4" t="b">

--- a/artfynd/A 48764-2025 artfynd.xlsx
+++ b/artfynd/A 48764-2025 artfynd.xlsx
@@ -801,10 +801,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129453566</v>
+        <v>129453553</v>
       </c>
       <c r="B3" t="n">
-        <v>4773</v>
+        <v>58097</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -812,32 +812,36 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100299</v>
+        <v>103015</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Thomsons trägnagare</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Cacotemnus thomsoni</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Kraatz, 1881)</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>ex.</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>adult</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
@@ -851,13 +855,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>473998</v>
+        <v>473651</v>
       </c>
       <c r="R3" t="n">
-        <v>6424257</v>
+        <v>6424350</v>
       </c>
       <c r="S3" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -886,7 +890,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>13:28</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -896,7 +900,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>13:28</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -923,10 +927,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129453553</v>
+        <v>129453566</v>
       </c>
       <c r="B4" t="n">
-        <v>58097</v>
+        <v>4773</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -934,36 +938,32 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103015</v>
+        <v>100299</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Thomsons trägnagare</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Cacotemnus thomsoni</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>adult</t>
+          <t>(Kraatz, 1881)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>ex.</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
@@ -977,13 +977,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>473651</v>
+        <v>473998</v>
       </c>
       <c r="R4" t="n">
-        <v>6424350</v>
+        <v>6424257</v>
       </c>
       <c r="S4" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1012,7 +1012,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>13:28</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1022,7 +1022,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>13:28</t>
         </is>
       </c>
       <c r="AD4" t="b">

--- a/artfynd/A 48764-2025 artfynd.xlsx
+++ b/artfynd/A 48764-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129452917</v>
       </c>
       <c r="B2" t="n">
-        <v>98724</v>
+        <v>98727</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -801,10 +801,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129453553</v>
+        <v>129453566</v>
       </c>
       <c r="B3" t="n">
-        <v>58097</v>
+        <v>4773</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -812,36 +812,32 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103015</v>
+        <v>100299</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Thomsons trägnagare</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Cacotemnus thomsoni</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>adult</t>
+          <t>(Kraatz, 1881)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>ex.</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
@@ -855,13 +851,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>473651</v>
+        <v>473998</v>
       </c>
       <c r="R3" t="n">
-        <v>6424350</v>
+        <v>6424257</v>
       </c>
       <c r="S3" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -890,7 +886,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>13:28</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -900,7 +896,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>13:28</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -927,10 +923,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129453566</v>
+        <v>129453553</v>
       </c>
       <c r="B4" t="n">
-        <v>4773</v>
+        <v>58097</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -938,32 +934,36 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100299</v>
+        <v>103015</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Thomsons trägnagare</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Cacotemnus thomsoni</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Kraatz, 1881)</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>ex.</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>adult</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
@@ -977,13 +977,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>473998</v>
+        <v>473651</v>
       </c>
       <c r="R4" t="n">
-        <v>6424257</v>
+        <v>6424350</v>
       </c>
       <c r="S4" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1012,7 +1012,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>13:28</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1022,7 +1022,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>13:28</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1301,7 +1301,7 @@
         <v>129452912</v>
       </c>
       <c r="B7" t="n">
-        <v>92268</v>
+        <v>92271</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1544,7 +1544,7 @@
         <v>129452920</v>
       </c>
       <c r="B9" t="n">
-        <v>98724</v>
+        <v>98727</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 48764-2025 artfynd.xlsx
+++ b/artfynd/A 48764-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY9"/>
+  <dimension ref="A1:AY19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -801,10 +801,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129453566</v>
+        <v>129453553</v>
       </c>
       <c r="B3" t="n">
-        <v>4773</v>
+        <v>58097</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -812,32 +812,36 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100299</v>
+        <v>103015</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Thomsons trägnagare</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Cacotemnus thomsoni</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Kraatz, 1881)</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>ex.</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>adult</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
@@ -851,13 +855,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>473998</v>
+        <v>473651</v>
       </c>
       <c r="R3" t="n">
-        <v>6424257</v>
+        <v>6424350</v>
       </c>
       <c r="S3" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -886,7 +890,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>13:28</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -896,7 +900,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>13:28</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -923,10 +927,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129453553</v>
+        <v>129453566</v>
       </c>
       <c r="B4" t="n">
-        <v>58097</v>
+        <v>4773</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -934,36 +938,32 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103015</v>
+        <v>100299</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Thomsons trägnagare</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Cacotemnus thomsoni</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>adult</t>
+          <t>(Kraatz, 1881)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>ex.</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
@@ -977,13 +977,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>473651</v>
+        <v>473998</v>
       </c>
       <c r="R4" t="n">
-        <v>6424350</v>
+        <v>6424257</v>
       </c>
       <c r="S4" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1012,7 +1012,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>13:28</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1022,7 +1022,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>13:28</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1665,6 +1665,1039 @@
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>129666316</v>
+      </c>
+      <c r="B10" t="n">
+        <v>96323</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>2180</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Blåmossa</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Leucobryum glaucum</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Jakobstorps gamla skogsbeten, Sm</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>473827</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6424431</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Jönköping</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Jönköping</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Gränna</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2025-11-09</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2025-11-09</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF10" t="inlineStr"/>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Marcus Hansson</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Marcus Hansson, henrik kullberg, anders berntsson</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>129666269</v>
+      </c>
+      <c r="B11" t="n">
+        <v>98727</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Jakobstorps gamla skogsbeten, Sm</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>473691</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6424387</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Jönköping</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Jönköping</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Gränna</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2025-11-09</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2025-11-09</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF11" t="inlineStr"/>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Marcus Hansson</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Marcus Hansson, henrik kullberg, anders berntsson</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>129666241</v>
+      </c>
+      <c r="B12" t="n">
+        <v>98727</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Jakobstorps gamla skogsbeten, Sm</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>473763</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6424532</v>
+      </c>
+      <c r="S12" t="n">
+        <v>10</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Jönköping</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Jönköping</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Gränna</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2025-11-09</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2025-11-09</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF12" t="inlineStr"/>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Marcus Hansson</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Marcus Hansson, henrik kullberg, anders berntsson</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>129666400</v>
+      </c>
+      <c r="B13" t="n">
+        <v>95963</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>2810</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Västlig hakmossa</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Rhytidiadelphus loreus</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Hedw.) Warnst.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Jakobstorps gamla skogsbeten, Sm</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>473849</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6424253</v>
+      </c>
+      <c r="S13" t="n">
+        <v>10</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Jönköping</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Jönköping</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Gränna</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2025-11-09</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2025-11-09</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF13" t="inlineStr"/>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Marcus Hansson</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Marcus Hansson, henrik kullberg, anders berntsson</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>129666170</v>
+      </c>
+      <c r="B14" t="n">
+        <v>98727</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Jakobstorps gamla skogsbeten, Sm</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>473978</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6424752</v>
+      </c>
+      <c r="S14" t="n">
+        <v>10</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Jönköping</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Jönköping</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Gränna</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2025-11-09</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2025-11-09</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF14" t="inlineStr"/>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Marcus Hansson</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Marcus Hansson, henrik kullberg, anders berntsson</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>129666346</v>
+      </c>
+      <c r="B15" t="n">
+        <v>97598</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Jakobstorps gamla skogsbeten, Sm</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>473844</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6424286</v>
+      </c>
+      <c r="S15" t="n">
+        <v>10</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Jönköping</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Jönköping</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Gränna</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2025-11-09</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2025-11-09</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF15" t="inlineStr"/>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Marcus Hansson</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Marcus Hansson, henrik kullberg, anders berntsson</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>129666029</v>
+      </c>
+      <c r="B16" t="n">
+        <v>95963</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>2810</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Västlig hakmossa</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Rhytidiadelphus loreus</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Hedw.) Warnst.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Jakobstorps gamla skogsbeten, Sm</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>473995</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6424753</v>
+      </c>
+      <c r="S16" t="n">
+        <v>10</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Jönköping</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Jönköping</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Gränna</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2025-11-09</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2025-11-09</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF16" t="inlineStr"/>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Marcus Hansson</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Marcus Hansson, henrik kullberg, anders berntsson</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>129666275</v>
+      </c>
+      <c r="B17" t="n">
+        <v>97598</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Jakobstorps gamla skogsbeten, Sm</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>473786</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6424453</v>
+      </c>
+      <c r="S17" t="n">
+        <v>10</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Jönköping</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Jönköping</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Gränna</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2025-11-09</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2025-11-09</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF17" t="inlineStr"/>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Marcus Hansson</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Marcus Hansson, henrik kullberg, anders berntsson</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>129666413</v>
+      </c>
+      <c r="B18" t="n">
+        <v>95963</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>2810</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Västlig hakmossa</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Rhytidiadelphus loreus</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(Hedw.) Warnst.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="N18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Jakobstorps gamla skogsbeten, Sm</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>473875</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6424398</v>
+      </c>
+      <c r="S18" t="n">
+        <v>10</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Jönköping</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Jönköping</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Gränna</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2025-11-09</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2025-11-09</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF18" t="inlineStr"/>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Marcus Hansson</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Marcus Hansson, henrik kullberg, anders berntsson</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>129666634</v>
+      </c>
+      <c r="B19" t="n">
+        <v>5177</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>100526</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Bronshjon</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Callidium coriaceum</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr"/>
+      <c r="N19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Jakobstorps gamla skogsbeten, Sm</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>473627</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6424599</v>
+      </c>
+      <c r="S19" t="n">
+        <v>10</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Jönköping</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Jönköping</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Gränna</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2025-11-09</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2025-11-09</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF19" t="inlineStr"/>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Marcus Hansson</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Marcus Hansson, henrik kullberg, anders berntsson</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 48764-2025 artfynd.xlsx
+++ b/artfynd/A 48764-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129452917</v>
       </c>
       <c r="B2" t="n">
-        <v>98727</v>
+        <v>98756</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -801,10 +801,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129453553</v>
+        <v>129453566</v>
       </c>
       <c r="B3" t="n">
-        <v>58097</v>
+        <v>4773</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -812,36 +812,32 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103015</v>
+        <v>100299</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Thomsons trägnagare</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Cacotemnus thomsoni</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>adult</t>
+          <t>(Kraatz, 1881)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>ex.</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
@@ -855,13 +851,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>473651</v>
+        <v>473998</v>
       </c>
       <c r="R3" t="n">
-        <v>6424350</v>
+        <v>6424257</v>
       </c>
       <c r="S3" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -890,7 +886,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>13:28</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -900,7 +896,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>13:28</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -927,10 +923,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129453566</v>
+        <v>129453553</v>
       </c>
       <c r="B4" t="n">
-        <v>4773</v>
+        <v>58100</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -938,32 +934,36 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100299</v>
+        <v>103015</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Thomsons trägnagare</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Cacotemnus thomsoni</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Kraatz, 1881)</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>ex.</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>adult</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
@@ -977,13 +977,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>473998</v>
+        <v>473651</v>
       </c>
       <c r="R4" t="n">
-        <v>6424257</v>
+        <v>6424350</v>
       </c>
       <c r="S4" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1012,7 +1012,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>13:28</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1022,7 +1022,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>13:28</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1301,7 +1301,7 @@
         <v>129452912</v>
       </c>
       <c r="B7" t="n">
-        <v>92271</v>
+        <v>92299</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1544,7 +1544,7 @@
         <v>129452920</v>
       </c>
       <c r="B9" t="n">
-        <v>98727</v>
+        <v>98756</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1670,7 +1670,7 @@
         <v>129666316</v>
       </c>
       <c r="B10" t="n">
-        <v>96323</v>
+        <v>96352</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1772,7 +1772,7 @@
         <v>129666269</v>
       </c>
       <c r="B11" t="n">
-        <v>98727</v>
+        <v>98756</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1878,7 +1878,7 @@
         <v>129666241</v>
       </c>
       <c r="B12" t="n">
-        <v>98727</v>
+        <v>98756</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1984,7 +1984,7 @@
         <v>129666400</v>
       </c>
       <c r="B13" t="n">
-        <v>95963</v>
+        <v>95992</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2086,7 +2086,7 @@
         <v>129666170</v>
       </c>
       <c r="B14" t="n">
-        <v>98727</v>
+        <v>98756</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2192,7 +2192,7 @@
         <v>129666346</v>
       </c>
       <c r="B15" t="n">
-        <v>97598</v>
+        <v>97627</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2294,7 +2294,7 @@
         <v>129666029</v>
       </c>
       <c r="B16" t="n">
-        <v>95963</v>
+        <v>95992</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2396,7 +2396,7 @@
         <v>129666275</v>
       </c>
       <c r="B17" t="n">
-        <v>97598</v>
+        <v>97627</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2498,7 +2498,7 @@
         <v>129666413</v>
       </c>
       <c r="B18" t="n">
-        <v>95963</v>
+        <v>95992</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>

--- a/artfynd/A 48764-2025 artfynd.xlsx
+++ b/artfynd/A 48764-2025 artfynd.xlsx
@@ -801,10 +801,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129453566</v>
+        <v>129453553</v>
       </c>
       <c r="B3" t="n">
-        <v>4773</v>
+        <v>58100</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -812,32 +812,36 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100299</v>
+        <v>103015</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Thomsons trägnagare</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Cacotemnus thomsoni</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Kraatz, 1881)</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>ex.</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>adult</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
@@ -851,13 +855,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>473998</v>
+        <v>473651</v>
       </c>
       <c r="R3" t="n">
-        <v>6424257</v>
+        <v>6424350</v>
       </c>
       <c r="S3" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -886,7 +890,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>13:28</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -896,7 +900,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>13:28</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -923,10 +927,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129453553</v>
+        <v>129453566</v>
       </c>
       <c r="B4" t="n">
-        <v>58100</v>
+        <v>4773</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -934,36 +938,32 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103015</v>
+        <v>100299</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Thomsons trägnagare</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Cacotemnus thomsoni</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>adult</t>
+          <t>(Kraatz, 1881)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>ex.</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
@@ -977,13 +977,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>473651</v>
+        <v>473998</v>
       </c>
       <c r="R4" t="n">
-        <v>6424350</v>
+        <v>6424257</v>
       </c>
       <c r="S4" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1012,7 +1012,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>13:28</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1022,7 +1022,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>13:28</t>
         </is>
       </c>
       <c r="AD4" t="b">

--- a/artfynd/A 48764-2025 artfynd.xlsx
+++ b/artfynd/A 48764-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129452917</v>
       </c>
       <c r="B2" t="n">
-        <v>98756</v>
+        <v>98768</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -801,10 +801,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129453553</v>
+        <v>129453566</v>
       </c>
       <c r="B3" t="n">
-        <v>58100</v>
+        <v>4773</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -812,36 +812,32 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103015</v>
+        <v>100299</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Thomsons trägnagare</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Cacotemnus thomsoni</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>adult</t>
+          <t>(Kraatz, 1881)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>ex.</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
@@ -855,13 +851,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>473651</v>
+        <v>473998</v>
       </c>
       <c r="R3" t="n">
-        <v>6424350</v>
+        <v>6424257</v>
       </c>
       <c r="S3" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -890,7 +886,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>13:28</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -900,7 +896,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>13:28</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -927,10 +923,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129453566</v>
+        <v>129453553</v>
       </c>
       <c r="B4" t="n">
-        <v>4773</v>
+        <v>58105</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -938,32 +934,36 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100299</v>
+        <v>103015</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Thomsons trägnagare</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Cacotemnus thomsoni</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Kraatz, 1881)</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>ex.</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>adult</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
@@ -977,13 +977,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>473998</v>
+        <v>473651</v>
       </c>
       <c r="R4" t="n">
-        <v>6424257</v>
+        <v>6424350</v>
       </c>
       <c r="S4" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1012,7 +1012,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>13:28</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1022,7 +1022,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>13:28</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1301,7 +1301,7 @@
         <v>129452912</v>
       </c>
       <c r="B7" t="n">
-        <v>92299</v>
+        <v>92305</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1544,7 +1544,7 @@
         <v>129452920</v>
       </c>
       <c r="B9" t="n">
-        <v>98756</v>
+        <v>98768</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1670,7 +1670,7 @@
         <v>129666316</v>
       </c>
       <c r="B10" t="n">
-        <v>96352</v>
+        <v>96364</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1772,7 +1772,7 @@
         <v>129666269</v>
       </c>
       <c r="B11" t="n">
-        <v>98756</v>
+        <v>98768</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1878,7 +1878,7 @@
         <v>129666241</v>
       </c>
       <c r="B12" t="n">
-        <v>98756</v>
+        <v>98768</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1984,7 +1984,7 @@
         <v>129666400</v>
       </c>
       <c r="B13" t="n">
-        <v>95992</v>
+        <v>96004</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2083,39 +2083,35 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129666170</v>
+        <v>129666346</v>
       </c>
       <c r="B14" t="n">
-        <v>98756</v>
+        <v>97639</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>221945</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
       <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr"/>
@@ -2126,10 +2122,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>473978</v>
+        <v>473844</v>
       </c>
       <c r="R14" t="n">
-        <v>6424752</v>
+        <v>6424286</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2189,35 +2185,39 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129666346</v>
+        <v>129666170</v>
       </c>
       <c r="B15" t="n">
-        <v>97627</v>
+        <v>98768</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
       <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr"/>
@@ -2228,10 +2228,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>473844</v>
+        <v>473978</v>
       </c>
       <c r="R15" t="n">
-        <v>6424286</v>
+        <v>6424752</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2294,7 +2294,7 @@
         <v>129666029</v>
       </c>
       <c r="B16" t="n">
-        <v>95992</v>
+        <v>96004</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2396,7 +2396,7 @@
         <v>129666275</v>
       </c>
       <c r="B17" t="n">
-        <v>97627</v>
+        <v>97639</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2498,7 +2498,7 @@
         <v>129666413</v>
       </c>
       <c r="B18" t="n">
-        <v>95992</v>
+        <v>96004</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>

--- a/artfynd/A 48764-2025 artfynd.xlsx
+++ b/artfynd/A 48764-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129452917</v>
       </c>
       <c r="B2" t="n">
-        <v>98768</v>
+        <v>98769</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -794,7 +794,7 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>William Rosén, Marcus Hansson, anders berntsson</t>
+          <t>William Rosén, anders berntsson, Marcus Hansson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
@@ -926,7 +926,7 @@
         <v>129453553</v>
       </c>
       <c r="B4" t="n">
-        <v>58105</v>
+        <v>58106</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1169,7 +1169,7 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>William Rosén, Marcus Hansson, anders berntsson</t>
+          <t>William Rosén, anders berntsson, Marcus Hansson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
@@ -1291,7 +1291,7 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>William Rosén, Marcus Hansson, anders berntsson</t>
+          <t>William Rosén, anders berntsson, Marcus Hansson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
@@ -1301,7 +1301,7 @@
         <v>129452912</v>
       </c>
       <c r="B7" t="n">
-        <v>92305</v>
+        <v>92306</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1412,7 +1412,7 @@
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>William Rosén, Marcus Hansson, anders berntsson</t>
+          <t>William Rosén, anders berntsson, Marcus Hansson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
@@ -1534,7 +1534,7 @@
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>William Rosén, Marcus Hansson, anders berntsson</t>
+          <t>William Rosén, anders berntsson, Marcus Hansson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
@@ -1544,7 +1544,7 @@
         <v>129452920</v>
       </c>
       <c r="B9" t="n">
-        <v>98768</v>
+        <v>98769</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1660,7 +1660,7 @@
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>William Rosén, Marcus Hansson, anders berntsson</t>
+          <t>William Rosén, anders berntsson, Marcus Hansson</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
@@ -1670,7 +1670,7 @@
         <v>129666316</v>
       </c>
       <c r="B10" t="n">
-        <v>96364</v>
+        <v>96365</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1772,7 +1772,7 @@
         <v>129666269</v>
       </c>
       <c r="B11" t="n">
-        <v>98768</v>
+        <v>98769</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1878,7 +1878,7 @@
         <v>129666241</v>
       </c>
       <c r="B12" t="n">
-        <v>98768</v>
+        <v>98769</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1984,7 +1984,7 @@
         <v>129666400</v>
       </c>
       <c r="B13" t="n">
-        <v>96004</v>
+        <v>96005</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2086,7 +2086,7 @@
         <v>129666346</v>
       </c>
       <c r="B14" t="n">
-        <v>97639</v>
+        <v>97640</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2188,7 +2188,7 @@
         <v>129666170</v>
       </c>
       <c r="B15" t="n">
-        <v>98768</v>
+        <v>98769</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2294,7 +2294,7 @@
         <v>129666029</v>
       </c>
       <c r="B16" t="n">
-        <v>96004</v>
+        <v>96005</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2396,7 +2396,7 @@
         <v>129666275</v>
       </c>
       <c r="B17" t="n">
-        <v>97639</v>
+        <v>97640</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2498,7 +2498,7 @@
         <v>129666413</v>
       </c>
       <c r="B18" t="n">
-        <v>96004</v>
+        <v>96005</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>

--- a/artfynd/A 48764-2025 artfynd.xlsx
+++ b/artfynd/A 48764-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129452917</v>
       </c>
       <c r="B2" t="n">
-        <v>98769</v>
+        <v>98774</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1301,7 +1301,7 @@
         <v>129452912</v>
       </c>
       <c r="B7" t="n">
-        <v>92306</v>
+        <v>92311</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1544,7 +1544,7 @@
         <v>129452920</v>
       </c>
       <c r="B9" t="n">
-        <v>98769</v>
+        <v>98774</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1667,35 +1667,39 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129666316</v>
+        <v>129666269</v>
       </c>
       <c r="B10" t="n">
-        <v>96365</v>
+        <v>98774</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>2180</v>
+        <v>220787</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
@@ -1706,10 +1710,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>473827</v>
+        <v>473691</v>
       </c>
       <c r="R10" t="n">
-        <v>6424431</v>
+        <v>6424387</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1762,46 +1766,42 @@
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Marcus Hansson, henrik kullberg, anders berntsson</t>
+          <t>anders berntsson, henrik kullberg, Marcus Hansson</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129666269</v>
+        <v>129666316</v>
       </c>
       <c r="B11" t="n">
-        <v>98769</v>
+        <v>96370</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>2180</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr"/>
@@ -1812,10 +1812,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>473691</v>
+        <v>473827</v>
       </c>
       <c r="R11" t="n">
-        <v>6424387</v>
+        <v>6424431</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1868,7 +1868,7 @@
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Marcus Hansson, henrik kullberg, anders berntsson</t>
+          <t>anders berntsson, henrik kullberg, Marcus Hansson</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
@@ -1878,7 +1878,7 @@
         <v>129666241</v>
       </c>
       <c r="B12" t="n">
-        <v>98769</v>
+        <v>98774</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1974,7 +1974,7 @@
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Marcus Hansson, henrik kullberg, anders berntsson</t>
+          <t>anders berntsson, henrik kullberg, Marcus Hansson</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
@@ -1984,7 +1984,7 @@
         <v>129666400</v>
       </c>
       <c r="B13" t="n">
-        <v>96005</v>
+        <v>96010</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2086,7 +2086,7 @@
         <v>129666346</v>
       </c>
       <c r="B14" t="n">
-        <v>97640</v>
+        <v>97645</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2188,7 +2188,7 @@
         <v>129666170</v>
       </c>
       <c r="B15" t="n">
-        <v>98769</v>
+        <v>98774</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2294,7 +2294,7 @@
         <v>129666029</v>
       </c>
       <c r="B16" t="n">
-        <v>96005</v>
+        <v>96010</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2396,7 +2396,7 @@
         <v>129666275</v>
       </c>
       <c r="B17" t="n">
-        <v>97640</v>
+        <v>97645</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2488,7 +2488,7 @@
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Marcus Hansson, henrik kullberg, anders berntsson</t>
+          <t>anders berntsson, henrik kullberg, Marcus Hansson</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
@@ -2498,7 +2498,7 @@
         <v>129666413</v>
       </c>
       <c r="B18" t="n">
-        <v>96005</v>
+        <v>96010</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2693,7 +2693,7 @@
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Marcus Hansson, henrik kullberg, anders berntsson</t>
+          <t>anders berntsson, henrik kullberg, Marcus Hansson</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>

--- a/artfynd/A 48764-2025 artfynd.xlsx
+++ b/artfynd/A 48764-2025 artfynd.xlsx
@@ -794,7 +794,7 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>William Rosén, anders berntsson, Marcus Hansson</t>
+          <t>William Rosén, Marcus Hansson, anders berntsson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
@@ -1169,7 +1169,7 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>William Rosén, anders berntsson, Marcus Hansson</t>
+          <t>William Rosén, Marcus Hansson, anders berntsson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
@@ -1291,7 +1291,7 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>William Rosén, anders berntsson, Marcus Hansson</t>
+          <t>William Rosén, Marcus Hansson, anders berntsson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
@@ -1412,7 +1412,7 @@
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>William Rosén, anders berntsson, Marcus Hansson</t>
+          <t>William Rosén, Marcus Hansson, anders berntsson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
@@ -1534,7 +1534,7 @@
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>William Rosén, anders berntsson, Marcus Hansson</t>
+          <t>William Rosén, Marcus Hansson, anders berntsson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
@@ -1660,7 +1660,7 @@
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>William Rosén, anders berntsson, Marcus Hansson</t>
+          <t>William Rosén, Marcus Hansson, anders berntsson</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
@@ -1766,7 +1766,7 @@
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>anders berntsson, henrik kullberg, Marcus Hansson</t>
+          <t>Marcus Hansson, henrik kullberg, anders berntsson</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
@@ -1868,7 +1868,7 @@
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>anders berntsson, henrik kullberg, Marcus Hansson</t>
+          <t>Marcus Hansson, henrik kullberg, anders berntsson</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
@@ -1974,7 +1974,7 @@
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>anders berntsson, henrik kullberg, Marcus Hansson</t>
+          <t>Marcus Hansson, henrik kullberg, anders berntsson</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
@@ -2083,35 +2083,39 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129666346</v>
+        <v>129666170</v>
       </c>
       <c r="B14" t="n">
-        <v>97645</v>
+        <v>98774</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
       <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr"/>
@@ -2122,10 +2126,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>473844</v>
+        <v>473978</v>
       </c>
       <c r="R14" t="n">
-        <v>6424286</v>
+        <v>6424752</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2185,39 +2189,35 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129666170</v>
+        <v>129666346</v>
       </c>
       <c r="B15" t="n">
-        <v>98774</v>
+        <v>97645</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220787</v>
+        <v>221945</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
       <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr"/>
@@ -2228,10 +2228,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>473978</v>
+        <v>473844</v>
       </c>
       <c r="R15" t="n">
-        <v>6424752</v>
+        <v>6424286</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2488,7 +2488,7 @@
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>anders berntsson, henrik kullberg, Marcus Hansson</t>
+          <t>Marcus Hansson, henrik kullberg, anders berntsson</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
@@ -2693,7 +2693,7 @@
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>anders berntsson, henrik kullberg, Marcus Hansson</t>
+          <t>Marcus Hansson, henrik kullberg, anders berntsson</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>

--- a/artfynd/A 48764-2025 artfynd.xlsx
+++ b/artfynd/A 48764-2025 artfynd.xlsx
@@ -794,17 +794,17 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>William Rosén, Marcus Hansson, anders berntsson</t>
+          <t>William Rosén, anders berntsson, Marcus Hansson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129453566</v>
+        <v>129453553</v>
       </c>
       <c r="B3" t="n">
-        <v>4773</v>
+        <v>58106</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -812,32 +812,36 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100299</v>
+        <v>103015</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Thomsons trägnagare</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Cacotemnus thomsoni</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Kraatz, 1881)</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>ex.</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>adult</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
@@ -851,13 +855,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>473998</v>
+        <v>473651</v>
       </c>
       <c r="R3" t="n">
-        <v>6424257</v>
+        <v>6424350</v>
       </c>
       <c r="S3" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -886,7 +890,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>13:28</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -896,7 +900,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>13:28</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -923,10 +927,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129453553</v>
+        <v>129453566</v>
       </c>
       <c r="B4" t="n">
-        <v>58106</v>
+        <v>4773</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -934,36 +938,32 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103015</v>
+        <v>100299</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Thomsons trägnagare</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Cacotemnus thomsoni</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>adult</t>
+          <t>(Kraatz, 1881)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>ex.</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
@@ -977,13 +977,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>473651</v>
+        <v>473998</v>
       </c>
       <c r="R4" t="n">
-        <v>6424350</v>
+        <v>6424257</v>
       </c>
       <c r="S4" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1012,7 +1012,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>13:28</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1022,7 +1022,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>13:28</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1169,7 +1169,7 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>William Rosén, Marcus Hansson, anders berntsson</t>
+          <t>William Rosén, anders berntsson, Marcus Hansson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
@@ -1291,7 +1291,7 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>William Rosén, Marcus Hansson, anders berntsson</t>
+          <t>William Rosén, anders berntsson, Marcus Hansson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
@@ -1412,7 +1412,7 @@
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>William Rosén, Marcus Hansson, anders berntsson</t>
+          <t>William Rosén, anders berntsson, Marcus Hansson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
@@ -1534,7 +1534,7 @@
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>William Rosén, Marcus Hansson, anders berntsson</t>
+          <t>William Rosén, anders berntsson, Marcus Hansson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
@@ -1660,7 +1660,7 @@
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>William Rosén, Marcus Hansson, anders berntsson</t>
+          <t>William Rosén, anders berntsson, Marcus Hansson</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
@@ -2182,7 +2182,7 @@
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Marcus Hansson, henrik kullberg, anders berntsson</t>
+          <t>anders berntsson, henrik kullberg, Marcus Hansson</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>

--- a/artfynd/A 48764-2025 artfynd.xlsx
+++ b/artfynd/A 48764-2025 artfynd.xlsx
@@ -801,10 +801,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129453553</v>
+        <v>129453566</v>
       </c>
       <c r="B3" t="n">
-        <v>58106</v>
+        <v>4773</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -812,36 +812,32 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103015</v>
+        <v>100299</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Thomsons trägnagare</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Cacotemnus thomsoni</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>adult</t>
+          <t>(Kraatz, 1881)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>ex.</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
@@ -855,13 +851,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>473651</v>
+        <v>473998</v>
       </c>
       <c r="R3" t="n">
-        <v>6424350</v>
+        <v>6424257</v>
       </c>
       <c r="S3" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -890,7 +886,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>13:28</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -900,7 +896,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>13:28</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -927,10 +923,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129453566</v>
+        <v>129453553</v>
       </c>
       <c r="B4" t="n">
-        <v>4773</v>
+        <v>58106</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -938,32 +934,36 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100299</v>
+        <v>103015</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Thomsons trägnagare</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Cacotemnus thomsoni</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Kraatz, 1881)</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>ex.</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>adult</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
@@ -977,13 +977,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>473998</v>
+        <v>473651</v>
       </c>
       <c r="R4" t="n">
-        <v>6424257</v>
+        <v>6424350</v>
       </c>
       <c r="S4" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1012,7 +1012,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>13:28</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1022,7 +1022,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>13:28</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1667,39 +1667,35 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129666269</v>
+        <v>129666316</v>
       </c>
       <c r="B10" t="n">
-        <v>98774</v>
+        <v>96370</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>2180</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
@@ -1710,10 +1706,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>473691</v>
+        <v>473827</v>
       </c>
       <c r="R10" t="n">
-        <v>6424387</v>
+        <v>6424431</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1766,42 +1762,46 @@
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Marcus Hansson, henrik kullberg, anders berntsson</t>
+          <t>anders berntsson, henrik kullberg, Marcus Hansson</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129666316</v>
+        <v>129666269</v>
       </c>
       <c r="B11" t="n">
-        <v>96370</v>
+        <v>98774</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>2180</v>
+        <v>220787</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr"/>
@@ -1812,10 +1812,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>473827</v>
+        <v>473691</v>
       </c>
       <c r="R11" t="n">
-        <v>6424431</v>
+        <v>6424387</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -2182,7 +2182,7 @@
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>anders berntsson, henrik kullberg, Marcus Hansson</t>
+          <t>Marcus Hansson, henrik kullberg, anders berntsson</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
@@ -2284,7 +2284,7 @@
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Marcus Hansson, henrik kullberg, anders berntsson</t>
+          <t>anders berntsson, henrik kullberg, Marcus Hansson</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>

--- a/artfynd/A 48764-2025 artfynd.xlsx
+++ b/artfynd/A 48764-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129452917</v>
       </c>
       <c r="B2" t="n">
-        <v>98774</v>
+        <v>98778</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -794,7 +794,7 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>William Rosén, anders berntsson, Marcus Hansson</t>
+          <t>William Rosén, Marcus Hansson, anders berntsson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
@@ -1169,7 +1169,7 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>William Rosén, anders berntsson, Marcus Hansson</t>
+          <t>William Rosén, Marcus Hansson, anders berntsson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
@@ -1291,7 +1291,7 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>William Rosén, anders berntsson, Marcus Hansson</t>
+          <t>William Rosén, Marcus Hansson, anders berntsson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
@@ -1301,7 +1301,7 @@
         <v>129452912</v>
       </c>
       <c r="B7" t="n">
-        <v>92311</v>
+        <v>92315</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1412,7 +1412,7 @@
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>William Rosén, anders berntsson, Marcus Hansson</t>
+          <t>William Rosén, Marcus Hansson, anders berntsson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
@@ -1534,7 +1534,7 @@
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>William Rosén, anders berntsson, Marcus Hansson</t>
+          <t>William Rosén, Marcus Hansson, anders berntsson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
@@ -1544,7 +1544,7 @@
         <v>129452920</v>
       </c>
       <c r="B9" t="n">
-        <v>98774</v>
+        <v>98778</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1660,42 +1660,46 @@
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>William Rosén, anders berntsson, Marcus Hansson</t>
+          <t>William Rosén, Marcus Hansson, anders berntsson</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129666316</v>
+        <v>129666269</v>
       </c>
       <c r="B10" t="n">
-        <v>96370</v>
+        <v>98778</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>2180</v>
+        <v>220787</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
@@ -1706,10 +1710,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>473827</v>
+        <v>473691</v>
       </c>
       <c r="R10" t="n">
-        <v>6424431</v>
+        <v>6424387</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1762,46 +1766,42 @@
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>anders berntsson, henrik kullberg, Marcus Hansson</t>
+          <t>Marcus Hansson, henrik kullberg, anders berntsson</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129666269</v>
+        <v>129666316</v>
       </c>
       <c r="B11" t="n">
-        <v>98774</v>
+        <v>96374</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>2180</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr"/>
@@ -1812,10 +1812,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>473691</v>
+        <v>473827</v>
       </c>
       <c r="R11" t="n">
-        <v>6424387</v>
+        <v>6424431</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1878,7 +1878,7 @@
         <v>129666241</v>
       </c>
       <c r="B12" t="n">
-        <v>98774</v>
+        <v>98778</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1984,7 +1984,7 @@
         <v>129666400</v>
       </c>
       <c r="B13" t="n">
-        <v>96010</v>
+        <v>96014</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2083,39 +2083,35 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129666170</v>
+        <v>129666346</v>
       </c>
       <c r="B14" t="n">
-        <v>98774</v>
+        <v>97649</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>221945</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
       <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr"/>
@@ -2126,10 +2122,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>473978</v>
+        <v>473844</v>
       </c>
       <c r="R14" t="n">
-        <v>6424752</v>
+        <v>6424286</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2189,35 +2185,39 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129666346</v>
+        <v>129666170</v>
       </c>
       <c r="B15" t="n">
-        <v>97645</v>
+        <v>98778</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
       <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr"/>
@@ -2228,10 +2228,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>473844</v>
+        <v>473978</v>
       </c>
       <c r="R15" t="n">
-        <v>6424286</v>
+        <v>6424752</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2294,7 +2294,7 @@
         <v>129666029</v>
       </c>
       <c r="B16" t="n">
-        <v>96010</v>
+        <v>96014</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2386,7 +2386,7 @@
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Marcus Hansson, henrik kullberg, anders berntsson</t>
+          <t>Marcus Hansson, anders berntsson, henrik kullberg</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
@@ -2396,7 +2396,7 @@
         <v>129666275</v>
       </c>
       <c r="B17" t="n">
-        <v>97645</v>
+        <v>97649</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2498,7 +2498,7 @@
         <v>129666413</v>
       </c>
       <c r="B18" t="n">
-        <v>96010</v>
+        <v>96014</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>

--- a/artfynd/A 48764-2025 artfynd.xlsx
+++ b/artfynd/A 48764-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129452917</v>
       </c>
       <c r="B2" t="n">
-        <v>98778</v>
+        <v>98780</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1301,7 +1301,7 @@
         <v>129452912</v>
       </c>
       <c r="B7" t="n">
-        <v>92315</v>
+        <v>92317</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1544,7 +1544,7 @@
         <v>129452920</v>
       </c>
       <c r="B9" t="n">
-        <v>98778</v>
+        <v>98780</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1667,39 +1667,35 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129666269</v>
+        <v>129666316</v>
       </c>
       <c r="B10" t="n">
-        <v>98778</v>
+        <v>96376</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>2180</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
@@ -1710,10 +1706,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>473691</v>
+        <v>473827</v>
       </c>
       <c r="R10" t="n">
-        <v>6424387</v>
+        <v>6424431</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1766,42 +1762,46 @@
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Marcus Hansson, henrik kullberg, anders berntsson</t>
+          <t>anders berntsson, henrik kullberg, Marcus Hansson</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129666316</v>
+        <v>129666269</v>
       </c>
       <c r="B11" t="n">
-        <v>96374</v>
+        <v>98780</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>2180</v>
+        <v>220787</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr"/>
@@ -1812,10 +1812,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>473827</v>
+        <v>473691</v>
       </c>
       <c r="R11" t="n">
-        <v>6424431</v>
+        <v>6424387</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1868,7 +1868,7 @@
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Marcus Hansson, henrik kullberg, anders berntsson</t>
+          <t>anders berntsson, henrik kullberg, Marcus Hansson</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
@@ -1878,7 +1878,7 @@
         <v>129666241</v>
       </c>
       <c r="B12" t="n">
-        <v>98778</v>
+        <v>98780</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1974,7 +1974,7 @@
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Marcus Hansson, henrik kullberg, anders berntsson</t>
+          <t>anders berntsson, henrik kullberg, Marcus Hansson</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
@@ -1984,7 +1984,7 @@
         <v>129666400</v>
       </c>
       <c r="B13" t="n">
-        <v>96014</v>
+        <v>96016</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2083,35 +2083,39 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129666346</v>
+        <v>129666170</v>
       </c>
       <c r="B14" t="n">
-        <v>97649</v>
+        <v>98780</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
       <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr"/>
@@ -2122,10 +2126,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>473844</v>
+        <v>473978</v>
       </c>
       <c r="R14" t="n">
-        <v>6424286</v>
+        <v>6424752</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2185,39 +2189,35 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129666170</v>
+        <v>129666346</v>
       </c>
       <c r="B15" t="n">
-        <v>98778</v>
+        <v>97651</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220787</v>
+        <v>221945</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
       <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr"/>
@@ -2228,10 +2228,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>473978</v>
+        <v>473844</v>
       </c>
       <c r="R15" t="n">
-        <v>6424752</v>
+        <v>6424286</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2284,7 +2284,7 @@
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>anders berntsson, henrik kullberg, Marcus Hansson</t>
+          <t>Marcus Hansson, henrik kullberg, anders berntsson</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
@@ -2294,7 +2294,7 @@
         <v>129666029</v>
       </c>
       <c r="B16" t="n">
-        <v>96014</v>
+        <v>96016</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2386,7 +2386,7 @@
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Marcus Hansson, anders berntsson, henrik kullberg</t>
+          <t>Marcus Hansson, henrik kullberg, anders berntsson</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
@@ -2396,7 +2396,7 @@
         <v>129666275</v>
       </c>
       <c r="B17" t="n">
-        <v>97649</v>
+        <v>97651</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2488,7 +2488,7 @@
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Marcus Hansson, henrik kullberg, anders berntsson</t>
+          <t>anders berntsson, henrik kullberg, Marcus Hansson</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
@@ -2498,7 +2498,7 @@
         <v>129666413</v>
       </c>
       <c r="B18" t="n">
-        <v>96014</v>
+        <v>96016</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>

--- a/artfynd/A 48764-2025 artfynd.xlsx
+++ b/artfynd/A 48764-2025 artfynd.xlsx
@@ -1667,35 +1667,39 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129666316</v>
+        <v>129666269</v>
       </c>
       <c r="B10" t="n">
-        <v>96376</v>
+        <v>98780</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>2180</v>
+        <v>220787</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
@@ -1706,10 +1710,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>473827</v>
+        <v>473691</v>
       </c>
       <c r="R10" t="n">
-        <v>6424431</v>
+        <v>6424387</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1769,39 +1773,35 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129666269</v>
+        <v>129666316</v>
       </c>
       <c r="B11" t="n">
-        <v>98780</v>
+        <v>96376</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>2180</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr"/>
@@ -1812,10 +1812,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>473691</v>
+        <v>473827</v>
       </c>
       <c r="R11" t="n">
-        <v>6424387</v>
+        <v>6424431</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>

--- a/artfynd/A 48764-2025 artfynd.xlsx
+++ b/artfynd/A 48764-2025 artfynd.xlsx
@@ -1667,39 +1667,35 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129666269</v>
+        <v>129666316</v>
       </c>
       <c r="B10" t="n">
-        <v>98780</v>
+        <v>96386</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>2180</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
@@ -1710,10 +1706,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>473691</v>
+        <v>473827</v>
       </c>
       <c r="R10" t="n">
-        <v>6424387</v>
+        <v>6424431</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1766,42 +1762,46 @@
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>anders berntsson, henrik kullberg, Marcus Hansson</t>
+          <t>Marcus Hansson, henrik kullberg, anders berntsson</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129666316</v>
+        <v>129666269</v>
       </c>
       <c r="B11" t="n">
-        <v>96376</v>
+        <v>98790</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>2180</v>
+        <v>220787</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr"/>
@@ -1812,10 +1812,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>473827</v>
+        <v>473691</v>
       </c>
       <c r="R11" t="n">
-        <v>6424431</v>
+        <v>6424387</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1868,7 +1868,7 @@
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>anders berntsson, henrik kullberg, Marcus Hansson</t>
+          <t>Marcus Hansson, henrik kullberg, anders berntsson</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
@@ -1878,7 +1878,7 @@
         <v>129666241</v>
       </c>
       <c r="B12" t="n">
-        <v>98780</v>
+        <v>98790</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1974,7 +1974,7 @@
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>anders berntsson, henrik kullberg, Marcus Hansson</t>
+          <t>Marcus Hansson, henrik kullberg, anders berntsson</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
@@ -1984,7 +1984,7 @@
         <v>129666400</v>
       </c>
       <c r="B13" t="n">
-        <v>96016</v>
+        <v>96026</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2083,39 +2083,35 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129666170</v>
+        <v>129666346</v>
       </c>
       <c r="B14" t="n">
-        <v>98780</v>
+        <v>97661</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>221945</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
       <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr"/>
@@ -2126,10 +2122,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>473978</v>
+        <v>473844</v>
       </c>
       <c r="R14" t="n">
-        <v>6424752</v>
+        <v>6424286</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2189,35 +2185,39 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129666346</v>
+        <v>129666170</v>
       </c>
       <c r="B15" t="n">
-        <v>97651</v>
+        <v>98790</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
       <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr"/>
@@ -2228,10 +2228,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>473844</v>
+        <v>473978</v>
       </c>
       <c r="R15" t="n">
-        <v>6424286</v>
+        <v>6424752</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2294,7 +2294,7 @@
         <v>129666029</v>
       </c>
       <c r="B16" t="n">
-        <v>96016</v>
+        <v>96026</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2396,7 +2396,7 @@
         <v>129666275</v>
       </c>
       <c r="B17" t="n">
-        <v>97651</v>
+        <v>97661</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2488,7 +2488,7 @@
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>anders berntsson, henrik kullberg, Marcus Hansson</t>
+          <t>Marcus Hansson, henrik kullberg, anders berntsson</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
@@ -2498,7 +2498,7 @@
         <v>129666413</v>
       </c>
       <c r="B18" t="n">
-        <v>96016</v>
+        <v>96026</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>

--- a/artfynd/A 48764-2025 artfynd.xlsx
+++ b/artfynd/A 48764-2025 artfynd.xlsx
@@ -1670,7 +1670,7 @@
         <v>129666316</v>
       </c>
       <c r="B10" t="n">
-        <v>96386</v>
+        <v>96390</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1772,7 +1772,7 @@
         <v>129666269</v>
       </c>
       <c r="B11" t="n">
-        <v>98790</v>
+        <v>98794</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1878,7 +1878,7 @@
         <v>129666241</v>
       </c>
       <c r="B12" t="n">
-        <v>98790</v>
+        <v>98794</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1984,7 +1984,7 @@
         <v>129666400</v>
       </c>
       <c r="B13" t="n">
-        <v>96026</v>
+        <v>96030</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2083,35 +2083,39 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129666346</v>
+        <v>129666170</v>
       </c>
       <c r="B14" t="n">
-        <v>97661</v>
+        <v>98794</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
       <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr"/>
@@ -2122,10 +2126,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>473844</v>
+        <v>473978</v>
       </c>
       <c r="R14" t="n">
-        <v>6424286</v>
+        <v>6424752</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2185,39 +2189,35 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129666170</v>
+        <v>129666346</v>
       </c>
       <c r="B15" t="n">
-        <v>98790</v>
+        <v>97665</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220787</v>
+        <v>221945</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
       <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr"/>
@@ -2228,10 +2228,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>473978</v>
+        <v>473844</v>
       </c>
       <c r="R15" t="n">
-        <v>6424752</v>
+        <v>6424286</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2294,7 +2294,7 @@
         <v>129666029</v>
       </c>
       <c r="B16" t="n">
-        <v>96026</v>
+        <v>96030</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2396,7 +2396,7 @@
         <v>129666275</v>
       </c>
       <c r="B17" t="n">
-        <v>97661</v>
+        <v>97665</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2498,7 +2498,7 @@
         <v>129666413</v>
       </c>
       <c r="B18" t="n">
-        <v>96026</v>
+        <v>96030</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>

--- a/artfynd/A 48764-2025 artfynd.xlsx
+++ b/artfynd/A 48764-2025 artfynd.xlsx
@@ -1670,7 +1670,7 @@
         <v>129666316</v>
       </c>
       <c r="B10" t="n">
-        <v>96390</v>
+        <v>96393</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1772,7 +1772,7 @@
         <v>129666269</v>
       </c>
       <c r="B11" t="n">
-        <v>98794</v>
+        <v>98797</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1878,7 +1878,7 @@
         <v>129666241</v>
       </c>
       <c r="B12" t="n">
-        <v>98794</v>
+        <v>98797</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1984,7 +1984,7 @@
         <v>129666400</v>
       </c>
       <c r="B13" t="n">
-        <v>96030</v>
+        <v>96033</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2086,7 +2086,7 @@
         <v>129666170</v>
       </c>
       <c r="B14" t="n">
-        <v>98794</v>
+        <v>98797</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2192,7 +2192,7 @@
         <v>129666346</v>
       </c>
       <c r="B15" t="n">
-        <v>97665</v>
+        <v>97668</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2294,7 +2294,7 @@
         <v>129666029</v>
       </c>
       <c r="B16" t="n">
-        <v>96030</v>
+        <v>96033</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2396,7 +2396,7 @@
         <v>129666275</v>
       </c>
       <c r="B17" t="n">
-        <v>97665</v>
+        <v>97668</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2498,7 +2498,7 @@
         <v>129666413</v>
       </c>
       <c r="B18" t="n">
-        <v>96030</v>
+        <v>96033</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>

--- a/artfynd/A 48764-2025 artfynd.xlsx
+++ b/artfynd/A 48764-2025 artfynd.xlsx
@@ -1667,35 +1667,39 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129666316</v>
+        <v>129666269</v>
       </c>
       <c r="B10" t="n">
-        <v>96393</v>
+        <v>98798</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>2180</v>
+        <v>220787</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
@@ -1706,10 +1710,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>473827</v>
+        <v>473691</v>
       </c>
       <c r="R10" t="n">
-        <v>6424431</v>
+        <v>6424387</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1769,39 +1773,35 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129666269</v>
+        <v>129666316</v>
       </c>
       <c r="B11" t="n">
-        <v>98797</v>
+        <v>96394</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>2180</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr"/>
@@ -1812,10 +1812,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>473691</v>
+        <v>473827</v>
       </c>
       <c r="R11" t="n">
-        <v>6424387</v>
+        <v>6424431</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1878,7 +1878,7 @@
         <v>129666241</v>
       </c>
       <c r="B12" t="n">
-        <v>98797</v>
+        <v>98798</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1984,7 +1984,7 @@
         <v>129666400</v>
       </c>
       <c r="B13" t="n">
-        <v>96033</v>
+        <v>96034</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2086,7 +2086,7 @@
         <v>129666170</v>
       </c>
       <c r="B14" t="n">
-        <v>98797</v>
+        <v>98798</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2192,7 +2192,7 @@
         <v>129666346</v>
       </c>
       <c r="B15" t="n">
-        <v>97668</v>
+        <v>97669</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2294,7 +2294,7 @@
         <v>129666029</v>
       </c>
       <c r="B16" t="n">
-        <v>96033</v>
+        <v>96034</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2396,7 +2396,7 @@
         <v>129666275</v>
       </c>
       <c r="B17" t="n">
-        <v>97668</v>
+        <v>97669</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2498,7 +2498,7 @@
         <v>129666413</v>
       </c>
       <c r="B18" t="n">
-        <v>96033</v>
+        <v>96034</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>

--- a/artfynd/A 48764-2025 artfynd.xlsx
+++ b/artfynd/A 48764-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY19"/>
+  <dimension ref="A1:AY25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,67 +675,52 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129452917</v>
+        <v>129666316</v>
       </c>
       <c r="B2" t="n">
-        <v>98780</v>
+        <v>96708</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>2180</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>114</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Jakobstorps gamla skogsbeten, Sm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>473789</v>
+        <v>473827</v>
       </c>
       <c r="R2" t="n">
-        <v>6424481</v>
+        <v>6424431</v>
       </c>
       <c r="S2" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -759,22 +744,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-10-31</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>11:47</t>
+          <t>2025-11-09</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2025-10-31</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>11:47</t>
+          <t>2025-11-09</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -783,28 +758,29 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>William Rosén</t>
+          <t>Marcus Hansson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>William Rosén, Marcus Hansson, anders berntsson</t>
+          <t>Marcus Hansson, henrik kullberg, anders berntsson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129453566</v>
+        <v>129666029</v>
       </c>
       <c r="B3" t="n">
-        <v>4773</v>
+        <v>96348</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -812,52 +788,41 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100299</v>
+        <v>2810</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Thomsons trägnagare</t>
+          <t>Västlig hakmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Cacotemnus thomsoni</t>
+          <t>Rhytidiadelphus loreus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Kraatz, 1881)</t>
+          <t>(Hedw.) Warnst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>ex.</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Jakobstorps gamla skogsbeten, Sm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>473998</v>
+        <v>473995</v>
       </c>
       <c r="R3" t="n">
-        <v>6424257</v>
+        <v>6424753</v>
       </c>
       <c r="S3" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -881,22 +846,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-10-31</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>13:28</t>
+          <t>2025-11-09</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2025-10-31</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>13:28</t>
+          <t>2025-11-09</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -905,28 +860,29 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>William Rosén</t>
+          <t>Marcus Hansson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>William Rosén, Marcus Hansson, anders berntsson</t>
+          <t>Marcus Hansson, henrik kullberg, anders berntsson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129453553</v>
+        <v>129666400</v>
       </c>
       <c r="B4" t="n">
-        <v>58106</v>
+        <v>96348</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -934,56 +890,41 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103015</v>
+        <v>2810</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Västlig hakmossa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Rhytidiadelphus loreus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Hedw.) Warnst.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Jakobstorps gamla skogsbeten, Sm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>473651</v>
+        <v>473849</v>
       </c>
       <c r="R4" t="n">
-        <v>6424350</v>
+        <v>6424253</v>
       </c>
       <c r="S4" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1007,22 +948,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-10-31</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>12:31</t>
+          <t>2025-11-09</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2025-10-31</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>12:31</t>
+          <t>2025-11-09</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1031,28 +962,29 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>William Rosén</t>
+          <t>Marcus Hansson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>William Rosén, Marcus Hansson, anders berntsson</t>
+          <t>Marcus Hansson, henrik kullberg, anders berntsson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129452908</v>
+        <v>129666413</v>
       </c>
       <c r="B5" t="n">
-        <v>5197</v>
+        <v>96348</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1060,52 +992,41 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>105930</v>
+        <v>2810</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Västlig hakmossa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Rhytidiadelphus loreus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hedw.) Warnst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>ex.</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Jakobstorps gamla skogsbeten, Sm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>473890</v>
+        <v>473875</v>
       </c>
       <c r="R5" t="n">
-        <v>6424445</v>
+        <v>6424398</v>
       </c>
       <c r="S5" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1129,27 +1050,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-10-31</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>11:23</t>
+          <t>2025-11-09</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2025-10-31</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>11:23</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>I bilden syns endast några av spåren vid fingret</t>
+          <t>2025-11-09</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1158,28 +1064,29 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>William Rosén</t>
+          <t>Marcus Hansson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>William Rosén, Marcus Hansson, anders berntsson</t>
+          <t>Marcus Hansson, henrik kullberg, anders berntsson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129452895</v>
+        <v>129452912</v>
       </c>
       <c r="B6" t="n">
-        <v>5177</v>
+        <v>92632</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1187,37 +1094,36 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100526</v>
+        <v>3298</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>ex.</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>mycel</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1226,10 +1132,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>473890</v>
+        <v>473834</v>
       </c>
       <c r="R6" t="n">
-        <v>6424445</v>
+        <v>6424442</v>
       </c>
       <c r="S6" t="n">
         <v>15</v>
@@ -1261,7 +1167,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>11:24</t>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1271,7 +1177,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>11:24</t>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1298,10 +1204,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129452912</v>
+        <v>129452896</v>
       </c>
       <c r="B7" t="n">
-        <v>92317</v>
+        <v>4775</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1309,36 +1215,37 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>3298</v>
+        <v>100299</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Thomsons trägnagare</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Cacotemnus thomsoni</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Kraatz, 1881)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr">
         <is>
-          <t>mycel</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+          <t>ex.</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1347,10 +1254,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>473834</v>
+        <v>473890</v>
       </c>
       <c r="R7" t="n">
-        <v>6424442</v>
+        <v>6424445</v>
       </c>
       <c r="S7" t="n">
         <v>15</v>
@@ -1382,7 +1289,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>11:33</t>
+          <t>11:24</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1392,7 +1299,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>11:33</t>
+          <t>11:24</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1419,10 +1326,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129452896</v>
+        <v>129453566</v>
       </c>
       <c r="B8" t="n">
-        <v>4773</v>
+        <v>4775</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1469,10 +1376,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>473890</v>
+        <v>473998</v>
       </c>
       <c r="R8" t="n">
-        <v>6424445</v>
+        <v>6424257</v>
       </c>
       <c r="S8" t="n">
         <v>15</v>
@@ -1504,7 +1411,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>11:24</t>
+          <t>13:28</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1514,7 +1421,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>11:24</t>
+          <t>13:28</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1541,47 +1448,43 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129452920</v>
+        <v>129452895</v>
       </c>
       <c r="B9" t="n">
-        <v>98780</v>
+        <v>5179</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>100526</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>ex.</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
@@ -1595,13 +1498,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>473731</v>
+        <v>473890</v>
       </c>
       <c r="R9" t="n">
-        <v>6424466</v>
+        <v>6424445</v>
       </c>
       <c r="S9" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1630,7 +1533,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>12:01</t>
+          <t>11:24</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1640,7 +1543,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>12:01</t>
+          <t>11:24</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1667,42 +1570,39 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129666269</v>
+        <v>129666634</v>
       </c>
       <c r="B10" t="n">
-        <v>98798</v>
+        <v>5179</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>100526</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1710,10 +1610,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>473691</v>
+        <v>473627</v>
       </c>
       <c r="R10" t="n">
-        <v>6424387</v>
+        <v>6424599</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1773,10 +1673,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129666316</v>
+        <v>129452892</v>
       </c>
       <c r="B11" t="n">
-        <v>96394</v>
+        <v>4781</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1784,41 +1684,52 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>2180</v>
+        <v>102306</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Duftschmid, 1825)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
-      <c r="N11" t="inlineStr"/>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Jakobstorps gamla skogsbeten, Sm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>473827</v>
+        <v>473969</v>
       </c>
       <c r="R11" t="n">
-        <v>6424431</v>
+        <v>6424442</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1842,12 +1753,22 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-09</t>
+          <t>2025-10-31</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2025-11-09</t>
+          <t>2025-10-31</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1856,75 +1777,85 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Marcus Hansson</t>
+          <t>William Rosén</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Marcus Hansson, henrik kullberg, anders berntsson</t>
+          <t>William Rosén, Marcus Hansson, anders berntsson</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129666241</v>
+        <v>129453553</v>
       </c>
       <c r="B12" t="n">
-        <v>98798</v>
+        <v>58327</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>103015</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
-      <c r="N12" t="inlineStr"/>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Jakobstorps gamla skogsbeten, Sm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>473763</v>
+        <v>473651</v>
       </c>
       <c r="R12" t="n">
-        <v>6424532</v>
+        <v>6424350</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1948,12 +1879,22 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-11-09</t>
+          <t>2025-10-31</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2025-11-09</t>
+          <t>2025-10-31</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1962,29 +1903,28 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
-      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Marcus Hansson</t>
+          <t>William Rosén</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Marcus Hansson, henrik kullberg, anders berntsson</t>
+          <t>William Rosén, Marcus Hansson, anders berntsson</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129666400</v>
+        <v>129452908</v>
       </c>
       <c r="B13" t="n">
-        <v>96034</v>
+        <v>5199</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1992,41 +1932,52 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>2810</v>
+        <v>105930</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Västlig hakmossa</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus loreus</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Hedw.) Warnst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
-      <c r="N13" t="inlineStr"/>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Jakobstorps gamla skogsbeten, Sm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>473849</v>
+        <v>473890</v>
       </c>
       <c r="R13" t="n">
-        <v>6424253</v>
+        <v>6424445</v>
       </c>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2050,12 +2001,27 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2025-11-09</t>
+          <t>2025-10-31</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>11:23</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2025-11-09</t>
+          <t>2025-10-31</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>11:23</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>I bilden syns endast några av spåren vid fingret</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2064,75 +2030,81 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
-      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Marcus Hansson</t>
+          <t>William Rosén</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Marcus Hansson, henrik kullberg, anders berntsson</t>
+          <t>William Rosén, Marcus Hansson, anders berntsson</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129666170</v>
+        <v>129453541</v>
       </c>
       <c r="B14" t="n">
-        <v>98798</v>
+        <v>101896</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>220075</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Gullpudra</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Chrysosplenium alternifolium</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr"/>
-      <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
-      <c r="N14" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Jakobstorps gamla skogsbeten, Sm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>473978</v>
+        <v>473630</v>
       </c>
       <c r="R14" t="n">
-        <v>6424752</v>
+        <v>6424209</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2156,12 +2128,22 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2025-11-09</t>
+          <t>2025-10-31</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2025-11-09</t>
+          <t>2025-10-31</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2170,71 +2152,85 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
-      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Marcus Hansson</t>
+          <t>William Rosén</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Marcus Hansson, henrik kullberg, anders berntsson</t>
+          <t>William Rosén, Marcus Hansson, anders berntsson</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129666346</v>
+        <v>129452909</v>
       </c>
       <c r="B15" t="n">
-        <v>97669</v>
+        <v>99118</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
-      <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
-      <c r="N15" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Jakobstorps gamla skogsbeten, Sm</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>473844</v>
+        <v>473837</v>
       </c>
       <c r="R15" t="n">
-        <v>6424286</v>
+        <v>6424469</v>
       </c>
       <c r="S15" t="n">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2258,12 +2254,22 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2025-11-09</t>
+          <t>2025-10-31</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2025-11-09</t>
+          <t>2025-10-31</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2272,71 +2278,85 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
-      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Marcus Hansson</t>
+          <t>William Rosén</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Marcus Hansson, henrik kullberg, anders berntsson</t>
+          <t>William Rosén, Marcus Hansson, anders berntsson</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129666029</v>
+        <v>129452917</v>
       </c>
       <c r="B16" t="n">
-        <v>96034</v>
+        <v>99118</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>2810</v>
+        <v>220787</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Västlig hakmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus loreus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Hedw.) Warnst.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
-      <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
-      <c r="N16" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>114</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Jakobstorps gamla skogsbeten, Sm</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>473995</v>
+        <v>473789</v>
       </c>
       <c r="R16" t="n">
-        <v>6424753</v>
+        <v>6424481</v>
       </c>
       <c r="S16" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2360,12 +2380,22 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2025-11-09</t>
+          <t>2025-10-31</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>11:47</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2025-11-09</t>
+          <t>2025-10-31</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>11:47</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2374,71 +2404,85 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
-      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Marcus Hansson</t>
+          <t>William Rosén</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Marcus Hansson, henrik kullberg, anders berntsson</t>
+          <t>William Rosén, Marcus Hansson, anders berntsson</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129666275</v>
+        <v>129452920</v>
       </c>
       <c r="B17" t="n">
-        <v>97669</v>
+        <v>99118</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
-      <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
-      <c r="N17" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Jakobstorps gamla skogsbeten, Sm</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>473786</v>
+        <v>473731</v>
       </c>
       <c r="R17" t="n">
-        <v>6424453</v>
+        <v>6424466</v>
       </c>
       <c r="S17" t="n">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2462,12 +2506,22 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2025-11-09</t>
+          <t>2025-10-31</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>12:01</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2025-11-09</t>
+          <t>2025-10-31</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>12:01</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2476,54 +2530,57 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
-      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Marcus Hansson</t>
+          <t>William Rosén</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Marcus Hansson, henrik kullberg, anders berntsson</t>
+          <t>William Rosén, Marcus Hansson, anders berntsson</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129666413</v>
+        <v>129666170</v>
       </c>
       <c r="B18" t="n">
-        <v>96034</v>
+        <v>99118</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>2810</v>
+        <v>220787</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Västlig hakmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus loreus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Hedw.) Warnst.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
       <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr"/>
       <c r="L18" t="inlineStr"/>
@@ -2534,10 +2591,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>473875</v>
+        <v>473978</v>
       </c>
       <c r="R18" t="n">
-        <v>6424398</v>
+        <v>6424752</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2597,39 +2654,42 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129666634</v>
+        <v>129666241</v>
       </c>
       <c r="B19" t="n">
-        <v>5177</v>
+        <v>99118</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100526</v>
+        <v>220787</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
       <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr"/>
       <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr"/>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
@@ -2637,10 +2697,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>473627</v>
+        <v>473763</v>
       </c>
       <c r="R19" t="n">
-        <v>6424599</v>
+        <v>6424532</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2697,6 +2757,628 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>129666269</v>
+      </c>
+      <c r="B20" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="N20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Jakobstorps gamla skogsbeten, Sm</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>473691</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6424387</v>
+      </c>
+      <c r="S20" t="n">
+        <v>10</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Jönköping</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Jönköping</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Gränna</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2025-11-09</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2025-11-09</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF20" t="inlineStr"/>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Marcus Hansson</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Marcus Hansson, henrik kullberg, anders berntsson</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>114751989</v>
+      </c>
+      <c r="B21" t="n">
+        <v>102419</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>221317</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Gullklöver</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Trifolium aureum</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>Pollich</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Örsnäs, Sm</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>474042</v>
+      </c>
+      <c r="R21" t="n">
+        <v>6424900</v>
+      </c>
+      <c r="S21" t="n">
+        <v>10</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Jönköping</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Jönköping</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Gränna</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2023-07-11</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2023-07-11</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Tomas Fasth</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Tomas Fasth</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>129666275</v>
+      </c>
+      <c r="B22" t="n">
+        <v>97983</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="N22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Jakobstorps gamla skogsbeten, Sm</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>473786</v>
+      </c>
+      <c r="R22" t="n">
+        <v>6424453</v>
+      </c>
+      <c r="S22" t="n">
+        <v>10</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Jönköping</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Jönköping</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Gränna</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2025-11-09</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2025-11-09</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF22" t="inlineStr"/>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Marcus Hansson</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Marcus Hansson, henrik kullberg, anders berntsson</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>129666346</v>
+      </c>
+      <c r="B23" t="n">
+        <v>97983</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="N23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Jakobstorps gamla skogsbeten, Sm</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>473844</v>
+      </c>
+      <c r="R23" t="n">
+        <v>6424286</v>
+      </c>
+      <c r="S23" t="n">
+        <v>10</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Jönköping</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Jönköping</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Gränna</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2025-11-09</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2025-11-09</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF23" t="inlineStr"/>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Marcus Hansson</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Marcus Hansson, henrik kullberg, anders berntsson</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>114751990</v>
+      </c>
+      <c r="B24" t="n">
+        <v>99754</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>222295</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Vårstarr</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Carex caryophyllea</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>Latourr.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Örsnäs, Sm</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>474042</v>
+      </c>
+      <c r="R24" t="n">
+        <v>6424900</v>
+      </c>
+      <c r="S24" t="n">
+        <v>10</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Jönköping</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Jönköping</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Gränna</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2023-07-11</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2023-07-11</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Tomas Fasth</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Tomas Fasth</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>129452914</v>
+      </c>
+      <c r="B25" t="n">
+        <v>97985</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>224363</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Vanlig revlummer</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum subsp. annotinum</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr"/>
+      <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Jakobstorps gamla skogsbeten, Sm</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>473822</v>
+      </c>
+      <c r="R25" t="n">
+        <v>6424491</v>
+      </c>
+      <c r="S25" t="n">
+        <v>18</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Jönköping</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Jönköping</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Gränna</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2025-10-31</t>
+        </is>
+      </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>11:45</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2025-10-31</t>
+        </is>
+      </c>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>11:45</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>William Rosén</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>William Rosén, Marcus Hansson, anders berntsson</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 48764-2025 artfynd.xlsx
+++ b/artfynd/A 48764-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY25"/>
+  <dimension ref="A1:AZ25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -774,6 +779,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129666316</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -876,6 +886,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129666029</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -978,6 +993,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129666400</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1080,6 +1100,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129666413</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1201,6 +1226,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129452912</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1323,6 +1353,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129452896</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1445,6 +1480,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129453566</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1567,6 +1607,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129452895</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1670,6 +1715,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129666634</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1792,6 +1842,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129452892</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1918,6 +1973,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129453553</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -2045,6 +2105,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129452908</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2167,6 +2232,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129453541</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2293,6 +2363,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129452909</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2419,6 +2494,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129452917</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2545,6 +2625,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129452920</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2651,6 +2736,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129666170</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2757,6 +2847,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129666241</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2863,6 +2958,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129666269</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2960,6 +3060,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114751989</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -3062,6 +3167,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129666275</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3164,6 +3274,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129666346</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3261,6 +3376,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114751990</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3379,8 +3499,39 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129452914</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>